--- a/artfynd/S 1692-2024 artfynd.xlsx
+++ b/artfynd/S 1692-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AZ70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554436</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554746</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554747</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554034</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553784</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553889</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1424,6 +1459,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/173703</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1540,6 +1580,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/177929</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1646,6 +1691,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554111</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554758</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1858,6 +1913,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554006</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1964,6 +2024,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554007</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2070,6 +2135,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554754</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2172,6 +2242,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75868479</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2278,6 +2353,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554305</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554307</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2490,6 +2575,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554309</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2596,6 +2686,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554320</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2702,6 +2797,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554759</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2808,6 +2908,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553932</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2914,6 +3019,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553848</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3020,6 +3130,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553849</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3126,6 +3241,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553724</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3232,6 +3352,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554733</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3333,6 +3458,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97730461</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3434,6 +3564,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97730463</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3540,6 +3675,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554382</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3646,6 +3786,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554383</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3752,6 +3897,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554385</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3858,6 +4008,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554736</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3974,6 +4129,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/834882</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4085,6 +4245,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/834883</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4201,6 +4366,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/695630</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4302,6 +4472,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97730459</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4408,6 +4583,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553635</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4514,6 +4694,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554753</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4620,6 +4805,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554727</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4736,6 +4926,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1502083</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4852,6 +5047,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2026091</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4958,6 +5158,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553572</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5064,6 +5269,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553628</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5170,6 +5380,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554740</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5276,6 +5491,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554741</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5382,6 +5602,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554742</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5488,6 +5713,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554743</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5594,6 +5824,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553720</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5700,6 +5935,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554728</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5816,6 +6056,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2262394</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5922,6 +6167,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553634</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6028,6 +6278,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98553983</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6134,6 +6389,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554628</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6236,6 +6496,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75868478</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6342,6 +6607,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554760</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6448,6 +6718,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554748</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6554,6 +6829,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554750</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6660,6 +6940,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554751</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6776,6 +7061,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2412422</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6886,6 +7176,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83270638</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6996,6 +7291,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83271696</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7097,6 +7397,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97730460</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7213,6 +7518,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4786428</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7324,6 +7634,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4896584</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7435,6 +7750,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4962894</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7546,6 +7866,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5244022</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7657,6 +7982,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5244620</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7768,6 +8098,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5244621</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7869,6 +8204,11 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97730462</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7967,6 +8307,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6277891</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8073,8 +8418,84 @@
           <t>LstF Lövskogsinventering 2021</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554765</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>